--- a/EasyEDA/APRS_Arduino_Tracker_Parts_List.xlsx
+++ b/EasyEDA/APRS_Arduino_Tracker_Parts_List.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ime\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0284B24-D70E-43C6-9600-E6F55D821017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E50870F9-35A7-4108-A4C2-45998A638022}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="3855"/>
   </bookViews>
   <sheets>
     <sheet name="APRS_Arduino_Tracker_Parts_List" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>Name</t>
   </si>
@@ -55,18 +54,12 @@
     <t>J1</t>
   </si>
   <si>
-    <t>Κλέμα πλακέτας 4pin</t>
-  </si>
-  <si>
     <t>BS170</t>
   </si>
   <si>
     <t>Q1</t>
   </si>
   <si>
-    <t>Τρανζίστορ</t>
-  </si>
-  <si>
     <t>100k</t>
   </si>
   <si>
@@ -109,22 +102,16 @@
     <t>RV1</t>
   </si>
   <si>
-    <t>Ποντεσιόμετρο ξαπλωτό</t>
-  </si>
-  <si>
     <t>SW</t>
   </si>
   <si>
     <t>SW1</t>
-  </si>
-  <si>
-    <t>Push button</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -988,7 +975,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08EF936D-A79E-4200-8282-3F8ABE376EB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1056,30 +1043,26 @@
       <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1">
         <v>2</v>
@@ -1091,7 +1074,7 @@
         <v>270</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
@@ -1100,10 +1083,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
@@ -1112,10 +1095,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
@@ -1124,10 +1107,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
@@ -1136,10 +1119,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
@@ -1148,10 +1131,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C13" s="1">
         <v>2</v>
@@ -1160,31 +1143,27 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1">
         <v>1</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1">
         <v>1</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="D15" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
